--- a/SQExcel.Portal/src/content/docs/ja/docs/images/input-sheet-builder-dialog/input-sheet-builder-dialog.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/input-sheet-builder-dialog/input-sheet-builder-dialog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\input-sheet-builder-dialog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\input-sheet-builder-dialog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33E8AB1-95A4-47F0-97DC-E738F3EE68E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8F709F-F561-4824-B09E-3AA874FFE0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="2490" windowWidth="18100" windowHeight="12490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="830" yWindow="200" windowWidth="20320" windowHeight="13110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input-sheet-builder-dialog" sheetId="3" r:id="rId1"/>
@@ -1194,519 +1194,6 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>131</xdr:row>
-      <xdr:rowOff>97117</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>152</xdr:row>
-      <xdr:rowOff>214925</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="図 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD4FA0DA-5577-0766-0558-A923185358DB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="463176" y="27656117"/>
-          <a:ext cx="10650071" cy="4981161"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>69879</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="17" name="グループ化 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D1FC17D-4A49-0530-88DF-B8CCAF767E63}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="926353"/>
-          <a:ext cx="8520057" cy="8175467"/>
-          <a:chOff x="469900" y="914400"/>
-          <a:chExt cx="8641080" cy="8070879"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="2" name="図 1">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB762E5E-B7D1-35D6-147C-E62FCB2FD8A3}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="914400"/>
-            <a:ext cx="8641080" cy="8070879"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="3" name="正方形/長方形 2">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F37E508-5E30-492C-9E6F-694CBF77993C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="567385" y="1512457"/>
-            <a:ext cx="8450010" cy="1393928"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="4" name="四角形: 角を丸くする 3">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A0F64B3-2AD6-4465-8B90-E8B088FB8608}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7022624" y="1637306"/>
-            <a:ext cx="470884" cy="265984"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>①</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="5" name="四角形: 角を丸くする 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{472E7684-CBCD-45B7-A344-94B75C30E2BE}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7022624" y="3194295"/>
-            <a:ext cx="470885" cy="264833"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>②</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="四角形: 角を丸くする 5">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49A8A367-CC72-4C18-8B2C-C884FBF97099}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="958374" y="4224755"/>
-            <a:ext cx="478008" cy="265984"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>③</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="9" name="正方形/長方形 8">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB1D2DC8-FEE7-4B5D-B30C-B78F0D6A5C69}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="567386" y="3097943"/>
-            <a:ext cx="8350056" cy="759965"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="10" name="正方形/長方形 9">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DCF4A42-B613-49E4-A972-6BD059427DA6}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="559887" y="3975345"/>
-            <a:ext cx="8350056" cy="4520433"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="16" name="四角形: 角を丸くする 15">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572DFAE9-4FF2-4198-8193-53E109322C4B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1790224" y="4224755"/>
-            <a:ext cx="478008" cy="265984"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>③</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -1730,7 +1217,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1774,7 +1261,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1817,8 +1304,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="463176" y="21769294"/>
-          <a:ext cx="8520057" cy="4345648"/>
+          <a:off x="469900" y="21488400"/>
+          <a:ext cx="8641080" cy="4291860"/>
           <a:chOff x="469900" y="21488400"/>
           <a:chExt cx="8641080" cy="4291860"/>
         </a:xfrm>
@@ -1837,7 +1324,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -1995,10 +1482,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="36" name="グループ化 35">
+        <xdr:cNvPr id="15" name="グループ化 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37D1EDC1-B119-5CE7-C275-E993519F0509}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{997E0850-FF9E-A4A7-0034-7590E2C72151}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2006,41 +1493,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="448235" y="36613354"/>
-          <a:ext cx="8520057" cy="8175467"/>
-          <a:chOff x="451597" y="33398013"/>
-          <a:chExt cx="8644442" cy="8070878"/>
+          <a:off x="451597" y="36141213"/>
+          <a:ext cx="8644442" cy="8070879"/>
+          <a:chOff x="451597" y="36141213"/>
+          <a:chExt cx="8644442" cy="8070879"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="32" name="図 31">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="14" name="グループ化 13">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67F8AF46-3F88-6133-2B5E-2F37C748C0AF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACBC3B3D-5D5D-3BE7-4DD3-5A78C0482FB4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="451597" y="33398013"/>
-            <a:ext cx="8644442" cy="8070878"/>
+            <a:off x="451597" y="36141213"/>
+            <a:ext cx="8644442" cy="8070879"/>
+            <a:chOff x="451597" y="36141213"/>
+            <a:chExt cx="8644442" cy="8070879"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="32" name="図 31">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67F8AF46-3F88-6133-2B5E-2F37C748C0AF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="451597" y="36141213"/>
+              <a:ext cx="8644442" cy="8070879"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="13" name="図 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C56AD11-890C-4065-9022-D18FF5DBCB47}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="507253" y="36208447"/>
+              <a:ext cx="252070" cy="225939"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="33" name="正方形/長方形 32">
@@ -2054,8 +1590,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="656664" y="34653070"/>
-            <a:ext cx="5034429" cy="558801"/>
+            <a:off x="657075" y="37397593"/>
+            <a:ext cx="5035947" cy="557077"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2109,8 +1645,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="626783" y="35811011"/>
-            <a:ext cx="6723903" cy="412377"/>
+            <a:off x="627624" y="38555598"/>
+            <a:ext cx="6724644" cy="411745"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2164,8 +1700,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="869203" y="39719624"/>
-            <a:ext cx="4102100" cy="322729"/>
+            <a:off x="869917" y="42464062"/>
+            <a:ext cx="4103587" cy="320935"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2236,7 +1772,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2251,125 +1787,6 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>216647</xdr:colOff>
-      <xdr:row>214</xdr:row>
-      <xdr:rowOff>14941</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>213659</xdr:colOff>
-      <xdr:row>235</xdr:row>
-      <xdr:rowOff>121327</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="41" name="グループ化 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82F0B33E-470C-AC4A-AF18-1C5FA38B18FB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="448235" y="49574823"/>
-          <a:ext cx="10650071" cy="4969739"/>
-          <a:chOff x="469900" y="45948600"/>
-          <a:chExt cx="10801350" cy="4906986"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="39" name="図 38">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D15EA227-6812-D04C-ECD0-64A10E2B8FBA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="45948600"/>
-            <a:ext cx="10801350" cy="4906986"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="40" name="正方形/長方形 39">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48DD3E20-4CEE-40ED-BEB4-6653293EABC7}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3476063" y="50366706"/>
-            <a:ext cx="4072218" cy="265954"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -2399,7 +1816,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2414,6 +1831,785 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>69879</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="12" name="グループ化 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52DE1B74-DDD9-3A95-097C-E67A1C6D9709}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="469900" y="914400"/>
+          <a:ext cx="8641080" cy="8070879"/>
+          <a:chOff x="469900" y="914400"/>
+          <a:chExt cx="8641080" cy="8070879"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="17" name="グループ化 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D1FC17D-4A49-0530-88DF-B8CCAF767E63}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="914400"/>
+            <a:ext cx="8641080" cy="8070879"/>
+            <a:chOff x="469900" y="914400"/>
+            <a:chExt cx="8641080" cy="8070879"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="図 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB762E5E-B7D1-35D6-147C-E62FCB2FD8A3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="914400"/>
+              <a:ext cx="8641080" cy="8070879"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="正方形/長方形 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F37E508-5E30-492C-9E6F-694CBF77993C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="567385" y="1512457"/>
+              <a:ext cx="8450010" cy="1393928"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="四角形: 角を丸くする 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A0F64B3-2AD6-4465-8B90-E8B088FB8608}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7022624" y="1637306"/>
+              <a:ext cx="470884" cy="265984"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>①</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="四角形: 角を丸くする 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{472E7684-CBCD-45B7-A344-94B75C30E2BE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7022624" y="3194295"/>
+              <a:ext cx="470885" cy="264833"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>②</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="四角形: 角を丸くする 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49A8A367-CC72-4C18-8B2C-C884FBF97099}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="958374" y="4224755"/>
+              <a:ext cx="478008" cy="265984"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9" name="正方形/長方形 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB1D2DC8-FEE7-4B5D-B30C-B78F0D6A5C69}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="567386" y="3097943"/>
+              <a:ext cx="8350056" cy="759965"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="10" name="正方形/長方形 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DCF4A42-B613-49E4-A972-6BD059427DA6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="559887" y="3975345"/>
+              <a:ext cx="8350056" cy="4520433"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="四角形: 角を丸くする 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572DFAE9-4FF2-4198-8193-53E109322C4B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1790224" y="4224755"/>
+              <a:ext cx="478008" cy="265984"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="8" name="図 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8B5C39F-03B8-4E25-9B8D-F34EB97755B9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="543560" y="959805"/>
+            <a:ext cx="251901" cy="225879"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>97117</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>214925</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="25" name="グループ化 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B27F42-7CC6-9743-6F0D-8F78AD568DD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="469900" y="30043717"/>
+          <a:ext cx="10801350" cy="4918408"/>
+          <a:chOff x="469900" y="30043717"/>
+          <a:chExt cx="10801350" cy="4918408"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="31" name="図 30">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD4FA0DA-5577-0766-0558-A923185358DB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="469900" y="30043717"/>
+            <a:ext cx="10801350" cy="4918408"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="24" name="図 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8450A8F-730E-7547-D27E-04AA8AF85108}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7874001" y="31242000"/>
+            <a:ext cx="3257550" cy="155121"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>216647</xdr:colOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>14941</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>213659</xdr:colOff>
+      <xdr:row>235</xdr:row>
+      <xdr:rowOff>121327</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="28" name="グループ化 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D106CB6-5A22-63E3-D281-D32D28136D91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="451597" y="48935341"/>
+          <a:ext cx="10804712" cy="4906986"/>
+          <a:chOff x="451597" y="48935341"/>
+          <a:chExt cx="10804712" cy="4906986"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="41" name="グループ化 40">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82F0B33E-470C-AC4A-AF18-1C5FA38B18FB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="451597" y="48935341"/>
+            <a:ext cx="10804712" cy="4906986"/>
+            <a:chOff x="469900" y="45948600"/>
+            <a:chExt cx="10801350" cy="4906986"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="39" name="図 38">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D15EA227-6812-D04C-ECD0-64A10E2B8FBA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="45948600"/>
+              <a:ext cx="10801350" cy="4906986"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="40" name="正方形/長方形 39">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48DD3E20-4CEE-40ED-BEB4-6653293EABC7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3476063" y="50366706"/>
+              <a:ext cx="4072218" cy="265954"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="27" name="図 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2A598AF-ADB2-818A-8AB4-98BA5F209407}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="6007101" y="50190401"/>
+            <a:ext cx="3625849" cy="205943"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
